--- a/rcads/data/xls/80_Persons.xlsx
+++ b/rcads/data/xls/80_Persons.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_80_Persons"/>
   </sheets>
   <definedNames>
-    <definedName name="_80_Persons">'_80_Persons'!$A$1:$D$111</definedName>
+    <definedName name="_80_Persons">'_80_Persons'!$A$1:$D$120</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2068,6 +2068,153 @@
         <v>0</v>
       </c>
     </row>
+    <row outlineLevel="0" r="112">
+      <c r="A112" s="0">
+        <v>113</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Anjali Joglekar</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="113">
+      <c r="A113" s="0">
+        <v>114</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Ujjwal Nene</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="114">
+      <c r="A114" s="0">
+        <v>115</v>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Bindu Patni</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="115">
+      <c r="A115" s="0">
+        <v>116</v>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Syethemba Nkosi</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>0000-0001-9174-2525</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="116">
+      <c r="A116" s="0">
+        <v>117</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Nondumiso Dlamini</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>0000-0002-0000-324X</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="117">
+      <c r="A117" s="0">
+        <v>118</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Truc Nguyen Thanh</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>0000-0002-2924-715X</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="118">
+      <c r="A118" s="0">
+        <v>119</v>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Tuyen Nguyen Thi Bich</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>0000-0002-7423-573X</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="119">
+      <c r="A119" s="0">
+        <v>120</v>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Thuy Nguyen Thi Nhu</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>0009-0009-2111-4887</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="120">
+      <c r="A120" s="0">
+        <v>121</v>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Thuoc Huynh Thi Bich</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>0009-0004-3243-6236</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
